--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:8001_{B305EEF1-6A78-44C5-91B2-8E6FFDAA2096}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59A6ECF-2843-4CCE-B11B-01F16FD35BF9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -176,6 +176,9 @@
   </si>
   <si>
     <t>AUGUST</t>
+  </si>
+  <si>
+    <t>NO TRIP</t>
   </si>
 </sst>
 </file>
@@ -408,7 +411,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -469,6 +472,7 @@
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1096,17 +1100,17 @@
       <c r="B11" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="39"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1126,12 +1130,20 @@
       <c r="B12" s="24">
         <v>46237</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
+      <c r="C12" s="28">
+        <v>248162.33</v>
+      </c>
+      <c r="D12" s="28">
+        <v>211801.58</v>
+      </c>
       <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
+      <c r="F12" s="28">
+        <v>648.41999999999996</v>
+      </c>
       <c r="G12" s="27"/>
-      <c r="H12" s="28"/>
+      <c r="H12" s="28">
+        <v>212450</v>
+      </c>
       <c r="I12" s="27"/>
       <c r="J12" s="28"/>
       <c r="K12" s="27"/>
@@ -1154,15 +1166,17 @@
       <c r="B13" s="24">
         <v>46238</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="27"/>
+      <c r="C13" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="39"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -1294,17 +1308,17 @@
       <c r="B18" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -1492,17 +1506,17 @@
       <c r="B25" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="7"/>
@@ -1690,17 +1704,17 @@
       <c r="B32" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="39"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="7"/>
@@ -1888,17 +1902,17 @@
       <c r="B39" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="39"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="7"/>
@@ -1942,15 +1956,15 @@
     <row r="41" spans="1:22" ht="15">
       <c r="A41" s="10"/>
       <c r="B41" s="29"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="38"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="39"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="7"/>
@@ -1966,15 +1980,15 @@
     <row r="42" spans="1:22" ht="15">
       <c r="A42" s="19"/>
       <c r="B42" s="29"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="38"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="38"/>
+      <c r="K42" s="39"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="7"/>
@@ -1994,11 +2008,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>0</v>
+        <v>248162.33</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>211801.58</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -2006,7 +2020,7 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>648.41999999999996</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
@@ -2014,7 +2028,7 @@
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>212450</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6025,7 +6039,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C41:K41"/>
     <mergeCell ref="C11:K11"/>
@@ -6033,6 +6047,7 @@
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="C32:K32"/>
     <mergeCell ref="C39:K39"/>
+    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6321,17 +6336,17 @@
       <c r="B11" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="39"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -6351,12 +6366,22 @@
       <c r="B12" s="24">
         <v>46237</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
+      <c r="C12" s="28">
+        <v>516071.33</v>
+      </c>
+      <c r="D12" s="28">
+        <v>436263.83</v>
+      </c>
       <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="28"/>
+      <c r="F12" s="28">
+        <v>662.17</v>
+      </c>
+      <c r="G12" s="27">
+        <v>3396</v>
+      </c>
+      <c r="H12" s="28">
+        <v>436926</v>
+      </c>
       <c r="I12" s="27"/>
       <c r="J12" s="28"/>
       <c r="K12" s="27"/>
@@ -6379,15 +6404,28 @@
       <c r="B13" s="24">
         <v>46238</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="27"/>
+      <c r="C13" s="28">
+        <v>347634.17</v>
+      </c>
+      <c r="D13" s="28">
+        <v>287025.17</v>
+      </c>
+      <c r="E13" s="27">
+        <v>211.17</v>
+      </c>
       <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="28"/>
+      <c r="G13" s="27">
+        <v>2004</v>
+      </c>
+      <c r="H13" s="28">
+        <v>286814</v>
+      </c>
       <c r="I13" s="27"/>
       <c r="J13" s="28"/>
-      <c r="K13" s="27"/>
+      <c r="K13" s="27">
+        <f>650*9</f>
+        <v>5850</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -6519,17 +6557,17 @@
       <c r="B18" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -6717,17 +6755,17 @@
       <c r="B25" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="7"/>
@@ -6915,17 +6953,17 @@
       <c r="B32" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="39"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="7"/>
@@ -7113,17 +7151,17 @@
       <c r="B39" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="39"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="7"/>
@@ -7167,15 +7205,15 @@
     <row r="41" spans="1:22" ht="15">
       <c r="A41" s="10"/>
       <c r="B41" s="29"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="38"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="39"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="7"/>
@@ -7191,15 +7229,15 @@
     <row r="42" spans="1:22" ht="15">
       <c r="A42" s="19"/>
       <c r="B42" s="29"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="38"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="38"/>
+      <c r="K42" s="39"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="7"/>
@@ -7219,27 +7257,27 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>0</v>
+        <v>863705.5</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>723289</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>211.17</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>662.17</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>723740</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -7251,7 +7289,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>0</v>
+        <v>5850</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -11545,17 +11583,17 @@
       <c r="B11" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="39"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -11575,15 +11613,27 @@
       <c r="B12" s="24">
         <v>46237</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="27"/>
+      <c r="C12" s="28">
+        <v>406307.13</v>
+      </c>
+      <c r="D12" s="28">
+        <v>337941.88</v>
+      </c>
+      <c r="E12" s="27">
+        <v>331.88</v>
+      </c>
       <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="28"/>
+      <c r="G12" s="27">
+        <v>1602</v>
+      </c>
+      <c r="H12" s="28">
+        <v>337610</v>
+      </c>
       <c r="I12" s="27"/>
       <c r="J12" s="28"/>
-      <c r="K12" s="27"/>
+      <c r="K12" s="27">
+        <v>50</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -11603,12 +11653,22 @@
       <c r="B13" s="24">
         <v>46238</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
+      <c r="C13" s="28">
+        <v>472049.21</v>
+      </c>
+      <c r="D13" s="28">
+        <v>397218.71</v>
+      </c>
       <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="28"/>
+      <c r="F13" s="36">
+        <v>122.29</v>
+      </c>
+      <c r="G13" s="27">
+        <v>3366</v>
+      </c>
+      <c r="H13" s="28">
+        <v>397341</v>
+      </c>
       <c r="I13" s="27"/>
       <c r="J13" s="28"/>
       <c r="K13" s="27"/>
@@ -11743,17 +11803,17 @@
       <c r="B18" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -11941,17 +12001,17 @@
       <c r="B25" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="7"/>
@@ -12139,17 +12199,17 @@
       <c r="B32" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="39"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="7"/>
@@ -12337,17 +12397,17 @@
       <c r="B39" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="39"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="7"/>
@@ -12391,15 +12451,15 @@
     <row r="41" spans="1:22" ht="15">
       <c r="A41" s="10"/>
       <c r="B41" s="29"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="38"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="39"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="7"/>
@@ -12415,15 +12475,15 @@
     <row r="42" spans="1:22" ht="15">
       <c r="A42" s="19"/>
       <c r="B42" s="29"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="38"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="38"/>
+      <c r="K42" s="39"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="7"/>
@@ -12443,27 +12503,27 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>0</v>
+        <v>878356.34000000008</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>735160.59000000008</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>331.88</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>122.29</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4968</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>734951</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12475,7 +12535,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59A6ECF-2843-4CCE-B11B-01F16FD35BF9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98570635-1480-4124-8EC1-6D4060D240A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1196,12 +1196,22 @@
       <c r="B14" s="24">
         <v>46239</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
+      <c r="C14" s="28">
+        <v>276596</v>
+      </c>
+      <c r="D14" s="28">
+        <v>237279.5</v>
+      </c>
       <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="28"/>
+      <c r="F14" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="27">
+        <v>2034</v>
+      </c>
+      <c r="H14" s="28">
+        <v>237280</v>
+      </c>
       <c r="I14" s="27"/>
       <c r="J14" s="28"/>
       <c r="K14" s="27"/>
@@ -2008,11 +2018,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>248162.33</v>
+        <v>524758.32999999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>211801.58</v>
+        <v>449081.07999999996</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -2020,15 +2030,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>648.41999999999996</v>
+        <v>648.91999999999996</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2034</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>212450</v>
+        <v>449730</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6445,12 +6455,22 @@
       <c r="B14" s="24">
         <v>46239</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
+      <c r="C14" s="28">
+        <v>271026.42</v>
+      </c>
+      <c r="D14" s="28">
+        <v>232251.42</v>
+      </c>
       <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="28"/>
+      <c r="F14" s="28">
+        <v>472.58</v>
+      </c>
+      <c r="G14" s="27">
+        <v>1818</v>
+      </c>
+      <c r="H14" s="28">
+        <v>232724</v>
+      </c>
       <c r="I14" s="27"/>
       <c r="J14" s="28"/>
       <c r="K14" s="27"/>
@@ -7257,11 +7277,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>863705.5</v>
+        <v>1134731.92</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>723289</v>
+        <v>955540.42</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -7269,15 +7289,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>662.17</v>
+        <v>1134.75</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>5400</v>
+        <v>7218</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>723740</v>
+        <v>956464</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -11691,15 +11711,17 @@
       <c r="B14" s="24">
         <v>46239</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="27"/>
+      <c r="C14" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="39"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -16534,7 +16556,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C41:K41"/>
     <mergeCell ref="C11:K11"/>
@@ -16542,6 +16564,7 @@
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="C32:K32"/>
     <mergeCell ref="C39:K39"/>
+    <mergeCell ref="C14:K14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98570635-1480-4124-8EC1-6D4060D240A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8CC6BE-5E07-4EDC-AD6A-59704427B848}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -69,12 +69,62 @@
         </r>
       </text>
     </comment>
+    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{5930818C-DECD-4D05-BD54-A31AEDDE5E22}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 11720</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K15" authorId="0" shapeId="0" xr:uid="{009EC669-73A1-46E2-84C3-48F2A94F08F9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+TICKET = 50
+PROMO = 4550</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -189,7 +239,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +351,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1234,15 +1297,17 @@
       <c r="B15" s="24">
         <v>46240</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="27"/>
+      <c r="C15" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="39"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -6049,7 +6114,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C41:K41"/>
     <mergeCell ref="C11:K11"/>
@@ -6058,6 +6123,7 @@
     <mergeCell ref="C32:K32"/>
     <mergeCell ref="C39:K39"/>
     <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C15:K15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6493,15 +6559,30 @@
       <c r="B15" s="24">
         <v>46240</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
+      <c r="C15" s="28">
+        <v>402717.5</v>
+      </c>
+      <c r="D15" s="28">
+        <v>267331.5</v>
+      </c>
       <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="27"/>
+      <c r="F15" s="36">
+        <v>934.5</v>
+      </c>
+      <c r="G15" s="27">
+        <v>2178</v>
+      </c>
+      <c r="H15" s="28">
+        <v>268266</v>
+      </c>
+      <c r="I15" s="27">
+        <v>67927</v>
+      </c>
       <c r="J15" s="28"/>
-      <c r="K15" s="27"/>
+      <c r="K15" s="27">
+        <f>50+4550</f>
+        <v>4600</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -7277,11 +7358,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>1134731.92</v>
+        <v>1537449.42</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>955540.42</v>
+        <v>1222871.92</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -7289,19 +7370,19 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>1134.75</v>
+        <v>2069.25</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>7218</v>
+        <v>9396</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>956464</v>
+        <v>1224730</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67927</v>
       </c>
       <c r="J43" s="14">
         <f t="shared" si="0"/>
@@ -7309,7 +7390,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>5850</v>
+        <v>10450</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -11741,15 +11822,27 @@
       <c r="B15" s="24">
         <v>46240</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27"/>
+      <c r="C15" s="28">
+        <v>318659.21000000002</v>
+      </c>
+      <c r="D15" s="28">
+        <v>267775.96000000002</v>
+      </c>
+      <c r="E15" s="27">
+        <v>276.95999999999998</v>
+      </c>
       <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="28"/>
+      <c r="G15" s="27">
+        <v>1896</v>
+      </c>
+      <c r="H15" s="28">
+        <v>267499</v>
+      </c>
       <c r="I15" s="27"/>
       <c r="J15" s="28"/>
-      <c r="K15" s="27"/>
+      <c r="K15" s="27">
+        <v>3250</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -12525,15 +12618,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>878356.34000000008</v>
+        <v>1197015.55</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>735160.59000000008</v>
+        <v>1002936.55</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>331.88</v>
+        <v>608.83999999999992</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -12541,11 +12634,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>4968</v>
+        <v>6864</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>734951</v>
+        <v>1002450</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12557,7 +12650,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>50</v>
+        <v>3300</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8CC6BE-5E07-4EDC-AD6A-59704427B848}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FA8959-63CF-428B-BFCB-FE0A9E747B74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1327,12 +1327,20 @@
       <c r="B16" s="24">
         <v>46241</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="27"/>
+      <c r="C16" s="28">
+        <v>408810.71</v>
+      </c>
+      <c r="D16" s="28">
+        <v>348709.46</v>
+      </c>
+      <c r="E16" s="27">
+        <v>284.45999999999998</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="27"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>348425</v>
+      </c>
       <c r="I16" s="27"/>
       <c r="J16" s="28"/>
       <c r="K16" s="27"/>
@@ -2083,15 +2091,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>524758.32999999996</v>
+        <v>933569.04</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>449081.07999999996</v>
+        <v>797790.54</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>284.45999999999998</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2103,7 +2111,7 @@
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>449730</v>
+        <v>798155</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6602,12 +6610,22 @@
       <c r="B16" s="24">
         <v>46241</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
+      <c r="C16" s="28">
+        <v>314974.21000000002</v>
+      </c>
+      <c r="D16" s="28">
+        <v>261753.46</v>
+      </c>
       <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="28"/>
+      <c r="F16" s="36">
+        <v>429.54</v>
+      </c>
+      <c r="G16" s="27">
+        <v>1224</v>
+      </c>
+      <c r="H16" s="28">
+        <v>262183</v>
+      </c>
       <c r="I16" s="27"/>
       <c r="J16" s="28"/>
       <c r="K16" s="27"/>
@@ -7358,11 +7376,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>1537449.42</v>
+        <v>1852423.63</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1222871.92</v>
+        <v>1484625.38</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -7370,15 +7388,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>2069.25</v>
+        <v>2498.79</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>9396</v>
+        <v>10620</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1224730</v>
+        <v>1486913</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -11862,12 +11880,22 @@
       <c r="B16" s="24">
         <v>46241</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
+      <c r="C16" s="28">
+        <v>383530.17</v>
+      </c>
+      <c r="D16" s="28">
+        <v>323368.92</v>
+      </c>
       <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="28"/>
+      <c r="F16" s="36">
+        <v>165.08</v>
+      </c>
+      <c r="G16" s="27">
+        <v>2406</v>
+      </c>
+      <c r="H16" s="28">
+        <v>323534</v>
+      </c>
       <c r="I16" s="27"/>
       <c r="J16" s="28"/>
       <c r="K16" s="27"/>
@@ -12618,11 +12646,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>1197015.55</v>
+        <v>1580545.72</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1002936.55</v>
+        <v>1326305.47</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -12630,15 +12658,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>122.29</v>
+        <v>287.37</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>6864</v>
+        <v>9270</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1002450</v>
+        <v>1325984</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7FA8959-63CF-428B-BFCB-FE0A9E747B74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3A90F1-07B1-4B52-B6E5-74EDBF82B2E0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -119,12 +119,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{A73D6420-F89B-473D-BA60-C237E8600787}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 11720</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1363,15 +1388,17 @@
       <c r="B17" s="24">
         <v>46242</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="27"/>
+      <c r="C17" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="39"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -6122,7 +6149,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C41:K41"/>
     <mergeCell ref="C11:K11"/>
@@ -6132,6 +6159,7 @@
     <mergeCell ref="C39:K39"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C15:K15"/>
+    <mergeCell ref="C17:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6648,14 +6676,26 @@
       <c r="B17" s="24">
         <v>46242</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="27"/>
+      <c r="C17" s="28">
+        <v>226955</v>
+      </c>
+      <c r="D17" s="28">
+        <v>260066.25</v>
+      </c>
+      <c r="E17" s="27">
+        <v>114.25</v>
+      </c>
       <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
+      <c r="G17" s="27">
+        <v>1350</v>
+      </c>
+      <c r="H17" s="28">
+        <v>259952</v>
+      </c>
       <c r="I17" s="27"/>
-      <c r="J17" s="28"/>
+      <c r="J17" s="28">
+        <v>67927</v>
+      </c>
       <c r="K17" s="27"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -7376,15 +7416,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>1852423.63</v>
+        <v>2079378.63</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1484625.38</v>
+        <v>1744691.63</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>211.17</v>
+        <v>325.41999999999996</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7392,11 +7432,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>10620</v>
+        <v>11970</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1486913</v>
+        <v>1746865</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -7404,7 +7444,7 @@
       </c>
       <c r="J43" s="14">
         <f t="shared" si="0"/>
-        <v>69862</v>
+        <v>137789</v>
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
@@ -11918,12 +11958,22 @@
       <c r="B17" s="24">
         <v>46242</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="27"/>
+      <c r="C17" s="28">
+        <v>303138.03999999998</v>
+      </c>
+      <c r="D17" s="28">
+        <v>274359.78999999998</v>
+      </c>
+      <c r="E17" s="27">
+        <v>30.79</v>
+      </c>
       <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="28"/>
+      <c r="G17" s="27">
+        <v>1944</v>
+      </c>
+      <c r="H17" s="28">
+        <v>274329</v>
+      </c>
       <c r="I17" s="27"/>
       <c r="J17" s="28"/>
       <c r="K17" s="27"/>
@@ -12646,15 +12696,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>1580545.72</v>
+        <v>1883683.76</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1326305.47</v>
+        <v>1600665.26</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>608.83999999999992</v>
+        <v>639.62999999999988</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -12662,11 +12712,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>9270</v>
+        <v>11214</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1325984</v>
+        <v>1600313</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3A90F1-07B1-4B52-B6E5-74EDBF82B2E0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E6472B-E2E5-4771-B5EF-DB3F01E9AC86}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E6472B-E2E5-4771-B5EF-DB3F01E9AC86}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCA2CD7-0A06-43EE-B47C-F00AC2B9E9CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1448,12 +1448,22 @@
       <c r="B19" s="24">
         <v>46244</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="27"/>
+      <c r="C19" s="28">
+        <v>256140.29</v>
+      </c>
+      <c r="D19" s="28">
+        <v>204925.79</v>
+      </c>
+      <c r="E19" s="27">
+        <v>142.29</v>
+      </c>
       <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
+      <c r="G19" s="27">
+        <v>1296</v>
+      </c>
+      <c r="H19" s="28">
+        <v>204783.5</v>
+      </c>
       <c r="I19" s="27"/>
       <c r="J19" s="28"/>
       <c r="K19" s="27"/>
@@ -2118,15 +2128,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>933569.04</v>
+        <v>1189709.33</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>797790.54</v>
+        <v>1002716.3300000001</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>284.45999999999998</v>
+        <v>426.75</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2134,11 +2144,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>2034</v>
+        <v>3330</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>798155</v>
+        <v>1002938.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6746,12 +6756,22 @@
       <c r="B19" s="24">
         <v>46244</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="27"/>
+      <c r="C19" s="28">
+        <v>380601.71</v>
+      </c>
+      <c r="D19" s="28">
+        <v>322742.21000000002</v>
+      </c>
+      <c r="E19" s="27">
+        <v>942.21</v>
+      </c>
       <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
+      <c r="G19" s="27">
+        <v>1974</v>
+      </c>
+      <c r="H19" s="28">
+        <v>321800</v>
+      </c>
       <c r="I19" s="27"/>
       <c r="J19" s="28"/>
       <c r="K19" s="27"/>
@@ -7416,15 +7436,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>2079378.63</v>
+        <v>2459980.34</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1744691.63</v>
+        <v>2067433.8399999999</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>325.41999999999996</v>
+        <v>1267.6300000000001</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7432,11 +7452,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>11970</v>
+        <v>13944</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1746865</v>
+        <v>2068665</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12026,15 +12046,27 @@
       <c r="B19" s="24">
         <v>46244</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="27"/>
+      <c r="C19" s="28">
+        <v>459783.13</v>
+      </c>
+      <c r="D19" s="28">
+        <v>379942.13</v>
+      </c>
+      <c r="E19" s="27">
+        <v>26.13</v>
+      </c>
       <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="28"/>
+      <c r="G19" s="27">
+        <v>3042</v>
+      </c>
+      <c r="H19" s="28">
+        <v>379916</v>
+      </c>
       <c r="I19" s="27"/>
       <c r="J19" s="28"/>
-      <c r="K19" s="27"/>
+      <c r="K19" s="27">
+        <v>26.13</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -12696,15 +12728,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>1883683.76</v>
+        <v>2343466.89</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1600665.26</v>
+        <v>1980607.3900000001</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>639.62999999999988</v>
+        <v>665.75999999999988</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -12712,11 +12744,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>11214</v>
+        <v>14256</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1600313</v>
+        <v>1980229</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12728,7 +12760,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>3300</v>
+        <v>3326.13</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BCA2CD7-0A06-43EE-B47C-F00AC2B9E9CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCE47B3-C256-44BA-A5A0-46CC964CB8F1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -39,6 +39,41 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{1F2BCCE8-8418-47A7-AFA5-79606EC47646}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+SI NO. 11698</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>User</author>
@@ -909,7 +944,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392DCC38-B676-43F3-B392-E571D3EDC2BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392DCC38-B676-43F3-B392-E571D3EDC2BC}">
   <dimension ref="A1:V279"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1486,13 +1521,23 @@
       <c r="B20" s="24">
         <v>46245</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="27"/>
+      <c r="C20" s="28">
+        <v>346704.58</v>
+      </c>
+      <c r="D20" s="28">
+        <v>199090.83</v>
+      </c>
+      <c r="E20" s="27">
+        <v>1251.83</v>
+      </c>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="27"/>
+      <c r="H20" s="28">
+        <v>197839</v>
+      </c>
+      <c r="I20" s="27">
+        <v>97987</v>
+      </c>
       <c r="J20" s="28"/>
       <c r="K20" s="27"/>
       <c r="L20" s="1"/>
@@ -2128,15 +2173,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1189709.33</v>
+        <v>1536413.9100000001</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1002716.3300000001</v>
+        <v>1201807.1600000001</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>426.75</v>
+        <v>1678.58</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2148,11 +2193,11 @@
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1002938.5</v>
+        <v>1200777.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>0</v>
+        <v>97987</v>
       </c>
       <c r="J43" s="14">
         <f t="shared" si="1"/>
@@ -6173,6 +6218,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6794,12 +6840,22 @@
       <c r="B20" s="24">
         <v>46245</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
+      <c r="C20" s="28">
+        <v>284254.75</v>
+      </c>
+      <c r="D20" s="28">
+        <v>233590</v>
+      </c>
       <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
+      <c r="F20" s="36">
+        <v>3762</v>
+      </c>
+      <c r="G20" s="27">
+        <v>1806</v>
+      </c>
+      <c r="H20" s="28">
+        <v>233590</v>
+      </c>
       <c r="I20" s="27"/>
       <c r="J20" s="28"/>
       <c r="K20" s="27"/>
@@ -7436,11 +7492,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>2459980.34</v>
+        <v>2744235.09</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2067433.8399999999</v>
+        <v>2301023.84</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -7448,15 +7504,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>2498.79</v>
+        <v>6260.79</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>13944</v>
+        <v>15750</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2068665</v>
+        <v>2302255</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12086,12 +12142,22 @@
       <c r="B20" s="24">
         <v>46245</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="27"/>
+      <c r="C20" s="28">
+        <v>345718.13</v>
+      </c>
+      <c r="D20" s="28">
+        <v>293230.88</v>
+      </c>
+      <c r="E20" s="27">
+        <v>752.88</v>
+      </c>
       <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
+      <c r="G20" s="27">
+        <v>1296</v>
+      </c>
+      <c r="H20" s="28">
+        <v>292478</v>
+      </c>
       <c r="I20" s="27"/>
       <c r="J20" s="28"/>
       <c r="K20" s="27"/>
@@ -12728,15 +12794,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>2343466.89</v>
+        <v>2689185.02</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1980607.3900000001</v>
+        <v>2273838.27</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>665.75999999999988</v>
+        <v>1418.6399999999999</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -12744,11 +12810,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>14256</v>
+        <v>15552</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1980229</v>
+        <v>2272707</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCE47B3-C256-44BA-A5A0-46CC964CB8F1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD80A95-95CA-4940-9F22-DEE45D6FE3BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -66,6 +66,31 @@
           <t xml:space="preserve">
 BALWARTE
 SI NO. 11698</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J21" authorId="0" shapeId="0" xr:uid="{EB85805D-BADB-48F9-BD84-1B85F1B732CA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+SI NO. 11426</t>
         </r>
       </text>
     </comment>
@@ -1559,14 +1584,26 @@
       <c r="B21" s="24">
         <v>46246</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="27"/>
+      <c r="C21" s="28">
+        <v>519146.42</v>
+      </c>
+      <c r="D21" s="28">
+        <v>521249.42</v>
+      </c>
+      <c r="E21" s="27">
+        <v>130.41999999999999</v>
+      </c>
       <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28"/>
+      <c r="G21" s="27">
+        <v>3402</v>
+      </c>
+      <c r="H21" s="28">
+        <v>521119</v>
+      </c>
       <c r="I21" s="27"/>
-      <c r="J21" s="28"/>
+      <c r="J21" s="28">
+        <v>82890</v>
+      </c>
       <c r="K21" s="27"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2173,15 +2210,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1536413.9100000001</v>
+        <v>2055560.33</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1201807.1600000001</v>
+        <v>1723056.58</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>1678.58</v>
+        <v>1809</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2189,11 +2226,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>3330</v>
+        <v>6732</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1200777.5</v>
+        <v>1721896.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -2201,7 +2238,7 @@
       </c>
       <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>82890</v>
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
@@ -6878,12 +6915,22 @@
       <c r="B21" s="24">
         <v>46246</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="27"/>
+      <c r="C21" s="28">
+        <v>286025.53999999998</v>
+      </c>
+      <c r="D21" s="28">
+        <v>246847.04</v>
+      </c>
+      <c r="E21" s="27">
+        <v>1795.04</v>
+      </c>
       <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28"/>
+      <c r="G21" s="27">
+        <v>1944</v>
+      </c>
+      <c r="H21" s="28">
+        <v>245052</v>
+      </c>
       <c r="I21" s="27"/>
       <c r="J21" s="28"/>
       <c r="K21" s="27"/>
@@ -7492,15 +7539,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>2744235.09</v>
+        <v>3030260.63</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2301023.84</v>
+        <v>2547870.88</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>1267.6300000000001</v>
+        <v>3062.67</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7508,11 +7555,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>15750</v>
+        <v>17694</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2302255</v>
+        <v>2547307</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12180,12 +12227,22 @@
       <c r="B21" s="24">
         <v>46246</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="27"/>
+      <c r="C21" s="28">
+        <v>271982.5</v>
+      </c>
+      <c r="D21" s="28">
+        <v>231602.5</v>
+      </c>
+      <c r="E21" s="27">
+        <v>641.5</v>
+      </c>
       <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28"/>
+      <c r="G21" s="27">
+        <v>720</v>
+      </c>
+      <c r="H21" s="28">
+        <v>230961</v>
+      </c>
       <c r="I21" s="27"/>
       <c r="J21" s="28"/>
       <c r="K21" s="27"/>
@@ -12794,15 +12851,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>2689185.02</v>
+        <v>2961167.52</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2273838.27</v>
+        <v>2505440.77</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>1418.6399999999999</v>
+        <v>2060.14</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -12810,11 +12867,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>15552</v>
+        <v>16272</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2272707</v>
+        <v>2503668</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD80A95-95CA-4940-9F22-DEE45D6FE3BA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B51825B-5CF5-4A12-B16A-FFDB0BF09296}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -91,6 +91,31 @@
           <t xml:space="preserve">
 BALWARTE
 SI NO. 11426</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{1370AED1-ACA0-49F5-BBC2-8FDAA1A83DD3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 11915</t>
         </r>
       </text>
     </comment>
@@ -1624,13 +1649,23 @@
       <c r="B22" s="24">
         <v>46247</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
+      <c r="C22" s="28">
+        <v>354423</v>
+      </c>
+      <c r="D22" s="28">
+        <v>238368</v>
+      </c>
       <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
+      <c r="F22" s="36">
+        <v>62</v>
+      </c>
       <c r="G22" s="27"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="27"/>
+      <c r="H22" s="28">
+        <v>238430</v>
+      </c>
+      <c r="I22" s="27">
+        <v>62655</v>
+      </c>
       <c r="J22" s="28"/>
       <c r="K22" s="27"/>
       <c r="L22" s="1"/>
@@ -2210,11 +2245,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2055560.33</v>
+        <v>2409983.33</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1723056.58</v>
+        <v>1961424.58</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -2222,7 +2257,7 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>648.91999999999996</v>
+        <v>710.92</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
@@ -2230,11 +2265,11 @@
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1721896.5</v>
+        <v>1960326.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>97987</v>
+        <v>160642</v>
       </c>
       <c r="J43" s="14">
         <f t="shared" si="1"/>
@@ -6953,12 +6988,22 @@
       <c r="B22" s="24">
         <v>46247</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="27"/>
+      <c r="C22" s="28">
+        <v>293011.42</v>
+      </c>
+      <c r="D22" s="28">
+        <v>248008.42</v>
+      </c>
+      <c r="E22" s="27">
+        <v>558.41999999999996</v>
+      </c>
       <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="28"/>
+      <c r="G22" s="27">
+        <v>1470</v>
+      </c>
+      <c r="H22" s="28">
+        <v>247450</v>
+      </c>
       <c r="I22" s="27"/>
       <c r="J22" s="28"/>
       <c r="K22" s="27"/>
@@ -7539,15 +7584,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>3030260.63</v>
+        <v>3323272.05</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2547870.88</v>
+        <v>2795879.3</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>3062.67</v>
+        <v>3621.09</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7555,11 +7600,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>17694</v>
+        <v>19164</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2547307</v>
+        <v>2794757</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12265,15 +12310,27 @@
       <c r="B22" s="24">
         <v>46247</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="27"/>
+      <c r="C22" s="28">
+        <v>391216.08</v>
+      </c>
+      <c r="D22" s="28">
+        <v>333530.83</v>
+      </c>
+      <c r="E22" s="27">
+        <v>23994.83</v>
+      </c>
       <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="28"/>
+      <c r="G22" s="27">
+        <v>2736</v>
+      </c>
+      <c r="H22" s="28">
+        <v>331136</v>
+      </c>
       <c r="I22" s="27"/>
       <c r="J22" s="28"/>
-      <c r="K22" s="27"/>
+      <c r="K22" s="27">
+        <v>50</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -12851,15 +12908,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>2961167.52</v>
+        <v>3352383.6</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2505440.77</v>
+        <v>2838971.6</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>2060.14</v>
+        <v>26054.97</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -12867,11 +12924,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>16272</v>
+        <v>19008</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2503668</v>
+        <v>2834804</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12883,7 +12940,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>3326.13</v>
+        <v>3376.13</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B51825B-5CF5-4A12-B16A-FFDB0BF09296}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166F1293-E678-4E08-999C-3AAD2E32CC7F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -116,6 +116,31 @@
           <t xml:space="preserve">
 SOUND CHECK
 SI NO. 11915</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K23" authorId="0" shapeId="0" xr:uid="{EA3E0649-5BB5-4253-8F35-B1507F865B84}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+FACOMA 2307
+</t>
         </r>
       </text>
     </comment>
@@ -1687,15 +1712,27 @@
       <c r="B23" s="24">
         <v>46248</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="27"/>
+      <c r="C23" s="28">
+        <v>340635.63</v>
+      </c>
+      <c r="D23" s="28">
+        <v>294058.2</v>
+      </c>
+      <c r="E23" s="27">
+        <v>646.70000000000005</v>
+      </c>
       <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="28"/>
+      <c r="G23" s="27">
+        <v>1326</v>
+      </c>
+      <c r="H23" s="28">
+        <v>293411.5</v>
+      </c>
       <c r="I23" s="27"/>
       <c r="J23" s="28"/>
-      <c r="K23" s="27"/>
+      <c r="K23" s="27">
+        <v>126.93</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="7"/>
@@ -2245,15 +2282,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2409983.33</v>
+        <v>2750618.96</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>1961424.58</v>
+        <v>2255482.7800000003</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>1809</v>
+        <v>2455.6999999999998</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2261,11 +2298,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>6732</v>
+        <v>8058</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>1960326.5</v>
+        <v>2253738</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -2277,7 +2314,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>0</v>
+        <v>126.93</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -7026,12 +7063,22 @@
       <c r="B23" s="24">
         <v>46248</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="27"/>
+      <c r="C23" s="28">
+        <v>230845.08</v>
+      </c>
+      <c r="D23" s="28">
+        <v>199091.58</v>
+      </c>
+      <c r="E23" s="27">
+        <v>5484.58</v>
+      </c>
       <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="28"/>
+      <c r="G23" s="27">
+        <v>1248</v>
+      </c>
+      <c r="H23" s="28">
+        <v>193607</v>
+      </c>
       <c r="I23" s="27"/>
       <c r="J23" s="28"/>
       <c r="K23" s="27"/>
@@ -7584,15 +7631,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>3323272.05</v>
+        <v>3554117.13</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2795879.3</v>
+        <v>2994970.88</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>3621.09</v>
+        <v>9105.67</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7600,11 +7647,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>19164</v>
+        <v>20412</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2794757</v>
+        <v>2988364</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12350,12 +12397,22 @@
       <c r="B23" s="24">
         <v>46248</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="27"/>
+      <c r="C23" s="28">
+        <v>481855.21</v>
+      </c>
+      <c r="D23" s="28">
+        <v>400846.21</v>
+      </c>
+      <c r="E23" s="27">
+        <v>14669.21</v>
+      </c>
       <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="28"/>
+      <c r="G23" s="27">
+        <v>3528</v>
+      </c>
+      <c r="H23" s="28">
+        <v>386177</v>
+      </c>
       <c r="I23" s="27"/>
       <c r="J23" s="28"/>
       <c r="K23" s="27"/>
@@ -12908,15 +12965,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>3352383.6</v>
+        <v>3834238.81</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2838971.6</v>
+        <v>3239817.81</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>26054.97</v>
+        <v>40724.18</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -12924,11 +12981,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>19008</v>
+        <v>22536</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2834804</v>
+        <v>3220981</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166F1293-E678-4E08-999C-3AAD2E32CC7F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087CE81B-1C85-4CE7-9774-D7D34A36B630}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -141,6 +141,31 @@
           <t xml:space="preserve">
 FACOMA 2307
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J24" authorId="0" shapeId="0" xr:uid="{4959BA85-B35A-4539-85F5-3FCD05684297}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK 
+S.I NO 11915</t>
         </r>
       </text>
     </comment>
@@ -1759,7 +1784,9 @@
       <c r="G24" s="27"/>
       <c r="H24" s="28"/>
       <c r="I24" s="27"/>
-      <c r="J24" s="28"/>
+      <c r="J24" s="28">
+        <v>62655</v>
+      </c>
       <c r="K24" s="27"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
@@ -2310,7 +2337,7 @@
       </c>
       <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v>82890</v>
+        <v>145545</v>
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
@@ -12435,12 +12462,22 @@
       <c r="B24" s="24">
         <v>46249</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
+      <c r="C24" s="28">
+        <v>502994.04</v>
+      </c>
+      <c r="D24" s="28">
+        <v>452669.79</v>
+      </c>
       <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="28"/>
+      <c r="F24" s="36">
+        <v>16374.21</v>
+      </c>
+      <c r="G24" s="27">
+        <v>3108</v>
+      </c>
+      <c r="H24" s="28">
+        <v>469044</v>
+      </c>
       <c r="I24" s="27"/>
       <c r="J24" s="28"/>
       <c r="K24" s="27"/>
@@ -12965,11 +13002,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>3834238.81</v>
+        <v>4337232.8499999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>3239817.81</v>
+        <v>3692487.6</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -12977,15 +13014,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>287.37</v>
+        <v>16661.579999999998</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>22536</v>
+        <v>25644</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>3220981</v>
+        <v>3690025</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087CE81B-1C85-4CE7-9774-D7D34A36B630}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1421076B-CE5B-40D3-AD33-9669C02C13E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -284,7 +284,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1837,12 +1837,22 @@
       <c r="B26" s="24">
         <v>46251</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="27"/>
+      <c r="C26" s="28">
+        <v>408615.21</v>
+      </c>
+      <c r="D26" s="28">
+        <v>300432.21000000002</v>
+      </c>
+      <c r="E26" s="27">
+        <v>394.71</v>
+      </c>
       <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
+      <c r="G26" s="27">
+        <v>2676</v>
+      </c>
+      <c r="H26" s="28">
+        <v>300037.5</v>
+      </c>
       <c r="I26" s="27"/>
       <c r="J26" s="28"/>
       <c r="K26" s="27"/>
@@ -2309,15 +2319,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2750618.96</v>
+        <v>3159234.17</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2255482.7800000003</v>
+        <v>2555914.9900000002</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>2455.6999999999998</v>
+        <v>2850.41</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2325,11 +2335,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>8058</v>
+        <v>10734</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2253738</v>
+        <v>2553775.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7128,15 +7138,17 @@
       <c r="B24" s="24">
         <v>46249</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="27"/>
+      <c r="C24" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="39"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="7"/>
@@ -7186,12 +7198,22 @@
       <c r="B26" s="24">
         <v>46251</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="27"/>
+      <c r="C26" s="28">
+        <v>410326.75</v>
+      </c>
+      <c r="D26" s="28">
+        <v>347772.25</v>
+      </c>
+      <c r="E26" s="27">
+        <v>184.25</v>
+      </c>
       <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
+      <c r="G26" s="27">
+        <v>2700</v>
+      </c>
+      <c r="H26" s="28">
+        <v>347588</v>
+      </c>
       <c r="I26" s="27"/>
       <c r="J26" s="28"/>
       <c r="K26" s="27"/>
@@ -7658,15 +7680,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>3554117.13</v>
+        <v>3964443.88</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2994970.88</v>
+        <v>3342743.13</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>9105.67</v>
+        <v>9289.92</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7674,11 +7696,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>20412</v>
+        <v>23112</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2988364</v>
+        <v>3335952</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -11689,7 +11711,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C18:K18"/>
@@ -11697,6 +11719,7 @@
     <mergeCell ref="C32:K32"/>
     <mergeCell ref="C39:K39"/>
     <mergeCell ref="C41:K41"/>
+    <mergeCell ref="C24:K24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -12530,15 +12553,27 @@
       <c r="B26" s="24">
         <v>46251</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
+      <c r="C26" s="28">
+        <v>507297</v>
+      </c>
+      <c r="D26" s="28">
+        <v>449946.25</v>
+      </c>
       <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
+      <c r="F26" s="27">
+        <v>745.75</v>
+      </c>
+      <c r="G26" s="27">
+        <v>1776</v>
+      </c>
+      <c r="H26" s="28">
+        <v>450692</v>
+      </c>
       <c r="I26" s="27"/>
       <c r="J26" s="28"/>
-      <c r="K26" s="27"/>
+      <c r="K26" s="27">
+        <v>50</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="15"/>
@@ -13002,11 +13037,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>4337232.8499999996</v>
+        <v>4844529.8499999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>3692487.6</v>
+        <v>4142433.85</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -13014,15 +13049,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>16661.579999999998</v>
+        <v>17407.329999999998</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>25644</v>
+        <v>27420</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>3690025</v>
+        <v>4140717</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -13034,7 +13069,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>3376.13</v>
+        <v>3426.13</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1421076B-CE5B-40D3-AD33-9669C02C13E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83542A8E-D8CA-41CC-9E31-5E089527755F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1875,12 +1875,22 @@
       <c r="B27" s="24">
         <v>46252</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="27"/>
+      <c r="C27" s="28">
+        <v>524789.17000000004</v>
+      </c>
+      <c r="D27" s="28">
+        <v>445312.42</v>
+      </c>
+      <c r="E27" s="27">
+        <v>17.420000000000002</v>
+      </c>
       <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="28"/>
+      <c r="G27" s="27">
+        <v>3312</v>
+      </c>
+      <c r="H27" s="28">
+        <v>445295</v>
+      </c>
       <c r="I27" s="27"/>
       <c r="J27" s="28"/>
       <c r="K27" s="27"/>
@@ -2319,15 +2329,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3159234.17</v>
+        <v>3684023.34</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>2555914.9900000002</v>
+        <v>3001227.41</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>2850.41</v>
+        <v>2867.83</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2335,11 +2345,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>10734</v>
+        <v>14046</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2553775.5</v>
+        <v>2999070.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7236,12 +7246,22 @@
       <c r="B27" s="24">
         <v>46252</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
+      <c r="C27" s="28">
+        <v>226309.88</v>
+      </c>
+      <c r="D27" s="28">
+        <v>190773.38</v>
+      </c>
       <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="28"/>
+      <c r="F27" s="36">
+        <v>143.63</v>
+      </c>
+      <c r="G27" s="27">
+        <v>1116</v>
+      </c>
+      <c r="H27" s="28">
+        <v>190917</v>
+      </c>
       <c r="I27" s="27"/>
       <c r="J27" s="28"/>
       <c r="K27" s="27"/>
@@ -7680,11 +7700,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>3964443.88</v>
+        <v>4190753.76</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>3342743.13</v>
+        <v>3533516.51</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -7692,15 +7712,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>6260.79</v>
+        <v>6404.42</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>23112</v>
+        <v>24228</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>3335952</v>
+        <v>3526869</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12560,7 +12580,7 @@
         <v>449946.25</v>
       </c>
       <c r="E26" s="27"/>
-      <c r="F26" s="27">
+      <c r="F26" s="36">
         <v>745.75</v>
       </c>
       <c r="G26" s="27">
@@ -12593,12 +12613,20 @@
       <c r="B27" s="24">
         <v>46252</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
+      <c r="C27" s="28">
+        <v>239538</v>
+      </c>
+      <c r="D27" s="28">
+        <v>203881.5</v>
+      </c>
       <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
+      <c r="F27" s="36">
+        <v>20.5</v>
+      </c>
       <c r="G27" s="27"/>
-      <c r="H27" s="28"/>
+      <c r="H27" s="28">
+        <v>203902</v>
+      </c>
       <c r="I27" s="27"/>
       <c r="J27" s="28"/>
       <c r="K27" s="27"/>
@@ -13037,11 +13065,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>4844529.8499999996</v>
+        <v>5084067.8499999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>4142433.85</v>
+        <v>4346315.3499999996</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -13049,7 +13077,7 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>17407.329999999998</v>
+        <v>17427.829999999998</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
@@ -13057,7 +13085,7 @@
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>4140717</v>
+        <v>4344619</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83542A8E-D8CA-41CC-9E31-5E089527755F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1926928-1D64-462D-B6DA-48334BC52FCD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -166,6 +166,31 @@
           <t xml:space="preserve">
 SOUND CHECK 
 S.I NO 11915</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{E777750E-057B-4D14-AAA0-8CA00C3DD2C5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+S.I NO 11943</t>
         </r>
       </text>
     </comment>
@@ -1913,13 +1938,23 @@
       <c r="B28" s="24">
         <v>46253</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="27"/>
+      <c r="C28" s="28">
+        <v>400721.17</v>
+      </c>
+      <c r="D28" s="28">
+        <v>296278.67</v>
+      </c>
+      <c r="E28" s="27">
+        <v>55.67</v>
+      </c>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="27"/>
+      <c r="H28" s="28">
+        <v>296223</v>
+      </c>
+      <c r="I28" s="27">
+        <v>49577</v>
+      </c>
       <c r="J28" s="28"/>
       <c r="K28" s="27"/>
       <c r="L28" s="1"/>
@@ -2329,15 +2364,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3684023.34</v>
+        <v>4084744.51</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>3001227.41</v>
+        <v>3297506.08</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>2867.83</v>
+        <v>2923.5</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2349,11 +2384,11 @@
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>2999070.5</v>
+        <v>3295293.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>160642</v>
+        <v>210219</v>
       </c>
       <c r="J43" s="14">
         <f t="shared" si="1"/>
@@ -7284,12 +7319,22 @@
       <c r="B28" s="24">
         <v>46253</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="27"/>
+      <c r="C28" s="28">
+        <v>254847.13</v>
+      </c>
+      <c r="D28" s="28">
+        <v>215214.13</v>
+      </c>
+      <c r="E28" s="27">
+        <v>14.13</v>
+      </c>
       <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="28"/>
+      <c r="G28" s="27">
+        <v>1944</v>
+      </c>
+      <c r="H28" s="28">
+        <v>215200</v>
+      </c>
       <c r="I28" s="27"/>
       <c r="J28" s="28"/>
       <c r="K28" s="27"/>
@@ -7700,15 +7745,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>4190753.76</v>
+        <v>4445600.8899999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>3533516.51</v>
+        <v>3748730.6399999997</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>9289.92</v>
+        <v>9304.0499999999993</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7716,11 +7761,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>24228</v>
+        <v>26172</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>3526869</v>
+        <v>3742069</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12649,12 +12694,20 @@
       <c r="B28" s="24">
         <v>46253</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="27"/>
+      <c r="C28" s="28">
+        <v>304334.21000000002</v>
+      </c>
+      <c r="D28" s="28">
+        <v>259718.21</v>
+      </c>
+      <c r="E28" s="27">
+        <v>40.21</v>
+      </c>
       <c r="F28" s="27"/>
       <c r="G28" s="27"/>
-      <c r="H28" s="28"/>
+      <c r="H28" s="28">
+        <v>259678</v>
+      </c>
       <c r="I28" s="27"/>
       <c r="J28" s="28"/>
       <c r="K28" s="27"/>
@@ -13065,15 +13118,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>5084067.8499999996</v>
+        <v>5388402.0599999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>4346315.3499999996</v>
+        <v>4606033.5599999996</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>40724.18</v>
+        <v>40764.39</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -13085,7 +13138,7 @@
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>4344619</v>
+        <v>4604297</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1926928-1D64-462D-B6DA-48334BC52FCD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7916E55C-D45E-4B1D-816B-5E4976C529E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -191,6 +191,57 @@
           <t xml:space="preserve">
 SOUND CHECK
 S.I NO 11943</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{F67220B6-D680-4606-8164-A76B1888ADFD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+S.I NO 11945</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="0" shapeId="0" xr:uid="{9CBE62F9-6D5C-4B47-A805-5785B9CD74F1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+S.I NO 11698
+</t>
         </r>
       </text>
     </comment>
@@ -1976,14 +2027,28 @@
       <c r="B29" s="24">
         <v>46254</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="27"/>
+      <c r="C29" s="28">
+        <v>660045.42000000004</v>
+      </c>
+      <c r="D29" s="28">
+        <v>574754.92000000004</v>
+      </c>
+      <c r="E29" s="27">
+        <v>659.92</v>
+      </c>
       <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="28"/>
+      <c r="G29" s="27">
+        <v>1296</v>
+      </c>
+      <c r="H29" s="28">
+        <v>574095</v>
+      </c>
+      <c r="I29" s="27">
+        <v>97893</v>
+      </c>
+      <c r="J29" s="28">
+        <v>97987</v>
+      </c>
       <c r="K29" s="27"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2364,15 +2429,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4084744.51</v>
+        <v>4744789.93</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>3297506.08</v>
+        <v>3872261</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>2923.5</v>
+        <v>3583.42</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2380,19 +2445,19 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>14046</v>
+        <v>15342</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>3295293.5</v>
+        <v>3869388.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>210219</v>
+        <v>308112</v>
       </c>
       <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v>145545</v>
+        <v>243532</v>
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
@@ -7357,12 +7422,22 @@
       <c r="B29" s="24">
         <v>46254</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
+      <c r="C29" s="28">
+        <v>79145.25</v>
+      </c>
+      <c r="D29" s="28">
+        <v>66773.25</v>
+      </c>
       <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="28"/>
+      <c r="F29" s="36">
+        <v>64.75</v>
+      </c>
+      <c r="G29" s="27">
+        <v>534</v>
+      </c>
+      <c r="H29" s="28">
+        <v>66838</v>
+      </c>
       <c r="I29" s="27"/>
       <c r="J29" s="28"/>
       <c r="K29" s="27"/>
@@ -7745,11 +7820,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>4445600.8899999997</v>
+        <v>4524746.1399999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>3748730.6399999997</v>
+        <v>3815503.8899999997</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -7757,15 +7832,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>6404.42</v>
+        <v>6469.17</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>26172</v>
+        <v>26706</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>3742069</v>
+        <v>3808907</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12730,15 +12805,25 @@
       <c r="B29" s="24">
         <v>46254</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
+      <c r="C29" s="28">
+        <v>481202</v>
+      </c>
+      <c r="D29" s="28">
+        <v>405814.5</v>
+      </c>
       <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
+      <c r="F29" s="36">
+        <v>62.5</v>
+      </c>
+      <c r="G29" s="27">
+        <v>3732</v>
+      </c>
       <c r="H29" s="28"/>
       <c r="I29" s="27"/>
       <c r="J29" s="28"/>
-      <c r="K29" s="27"/>
+      <c r="K29" s="27">
+        <v>50</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="7"/>
@@ -13118,11 +13203,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>5388402.0599999996</v>
+        <v>5869604.0599999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>4606033.5599999996</v>
+        <v>5011848.0599999996</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -13130,11 +13215,11 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>17427.829999999998</v>
+        <v>17490.329999999998</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>27420</v>
+        <v>31152</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
@@ -13150,7 +13235,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>3426.13</v>
+        <v>3476.13</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7916E55C-D45E-4B1D-816B-5E4976C529E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C11F2E-5F72-4005-ACB0-33C25F997DFE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -2069,15 +2069,17 @@
       <c r="B30" s="24">
         <v>46255</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="27"/>
+      <c r="C30" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="39"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="7"/>
@@ -2097,15 +2099,17 @@
       <c r="B31" s="24">
         <v>46256</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="27"/>
+      <c r="C31" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="39"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="15"/>
@@ -6460,7 +6464,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C41:K41"/>
     <mergeCell ref="C11:K11"/>
@@ -6471,6 +6475,8 @@
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C15:K15"/>
     <mergeCell ref="C17:K17"/>
+    <mergeCell ref="C30:K30"/>
+    <mergeCell ref="C31:K31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -7460,12 +7466,22 @@
       <c r="B30" s="24">
         <v>46255</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="27"/>
+      <c r="C30" s="28">
+        <v>355218</v>
+      </c>
+      <c r="D30" s="28">
+        <v>292870.5</v>
+      </c>
+      <c r="E30" s="27">
+        <v>4.5</v>
+      </c>
       <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="28"/>
+      <c r="G30" s="27">
+        <v>2010</v>
+      </c>
+      <c r="H30" s="28">
+        <v>292866</v>
+      </c>
       <c r="I30" s="27"/>
       <c r="J30" s="28"/>
       <c r="K30" s="27"/>
@@ -7488,15 +7504,17 @@
       <c r="B31" s="24">
         <v>46256</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="27"/>
+      <c r="C31" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="39"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="15"/>
@@ -7820,15 +7838,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>4524746.1399999997</v>
+        <v>4879964.1399999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>3815503.8899999997</v>
+        <v>4108374.3899999997</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>9304.0499999999993</v>
+        <v>9308.5499999999993</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7836,11 +7854,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>26706</v>
+        <v>28716</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>3808907</v>
+        <v>4101773</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -11851,7 +11869,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C18:K18"/>
@@ -11860,6 +11878,7 @@
     <mergeCell ref="C39:K39"/>
     <mergeCell ref="C41:K41"/>
     <mergeCell ref="C24:K24"/>
+    <mergeCell ref="C31:K31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -12843,12 +12862,22 @@
       <c r="B30" s="24">
         <v>46255</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
+      <c r="C30" s="28">
+        <v>421825</v>
+      </c>
+      <c r="D30" s="28">
+        <v>373692.25</v>
+      </c>
       <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="28"/>
+      <c r="F30" s="28">
+        <v>918.75</v>
+      </c>
+      <c r="G30" s="27">
+        <v>300</v>
+      </c>
+      <c r="H30" s="28">
+        <v>374611</v>
+      </c>
       <c r="I30" s="27"/>
       <c r="J30" s="28"/>
       <c r="K30" s="27"/>
@@ -12871,15 +12900,17 @@
       <c r="B31" s="24">
         <v>46256</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="27"/>
+      <c r="C31" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="39"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="15"/>
@@ -13203,11 +13234,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>5869604.0599999996</v>
+        <v>6291429.0599999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>5011848.0599999996</v>
+        <v>5385540.3099999996</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -13215,15 +13246,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>17490.329999999998</v>
+        <v>18409.079999999998</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>31152</v>
+        <v>31452</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>4604297</v>
+        <v>4978908</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -17234,7 +17265,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C41:K41"/>
     <mergeCell ref="C11:K11"/>
@@ -17243,6 +17274,7 @@
     <mergeCell ref="C32:K32"/>
     <mergeCell ref="C39:K39"/>
     <mergeCell ref="C14:K14"/>
+    <mergeCell ref="C31:K31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C11F2E-5F72-4005-ACB0-33C25F997DFE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0DFA4E-E12A-4159-A8AF-0012881B6A54}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -245,6 +245,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="J31" authorId="0" shapeId="0" xr:uid="{E7AB9747-BE8F-479A-8C9C-38F38A519B3E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+S.I NO 11943
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -360,7 +386,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -2099,17 +2125,17 @@
       <c r="B31" s="24">
         <v>46256</v>
       </c>
-      <c r="C31" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="39"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="28">
+        <v>49577</v>
+      </c>
+      <c r="K31" s="27"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="15"/>
@@ -2159,12 +2185,22 @@
       <c r="B33" s="24">
         <v>46258</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="27"/>
+      <c r="C33" s="28">
+        <v>737255</v>
+      </c>
+      <c r="D33" s="28">
+        <v>622931.5</v>
+      </c>
+      <c r="E33" s="27">
+        <v>2845.5</v>
+      </c>
       <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="28"/>
+      <c r="G33" s="27">
+        <v>5304</v>
+      </c>
+      <c r="H33" s="28">
+        <v>660086</v>
+      </c>
       <c r="I33" s="27"/>
       <c r="J33" s="28"/>
       <c r="K33" s="27"/>
@@ -2433,15 +2469,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4744789.93</v>
+        <v>5482044.9299999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>3872261</v>
+        <v>4495192.5</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>3583.42</v>
+        <v>6428.92</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2449,11 +2485,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>15342</v>
+        <v>20646</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>3869388.5</v>
+        <v>4529474.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -2461,7 +2497,7 @@
       </c>
       <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v>243532</v>
+        <v>293109</v>
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
@@ -6464,7 +6500,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C41:K41"/>
     <mergeCell ref="C11:K11"/>
@@ -6476,7 +6512,6 @@
     <mergeCell ref="C15:K15"/>
     <mergeCell ref="C17:K17"/>
     <mergeCell ref="C30:K30"/>
-    <mergeCell ref="C31:K31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -7564,12 +7599,22 @@
       <c r="B33" s="24">
         <v>46258</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="27"/>
+      <c r="C33" s="28">
+        <v>297905.78999999998</v>
+      </c>
+      <c r="D33" s="28">
+        <v>252974.79</v>
+      </c>
+      <c r="E33" s="27">
+        <v>102.79</v>
+      </c>
       <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="28"/>
+      <c r="G33" s="27">
+        <v>2148</v>
+      </c>
+      <c r="H33" s="28">
+        <v>252872</v>
+      </c>
       <c r="I33" s="27"/>
       <c r="J33" s="28"/>
       <c r="K33" s="27"/>
@@ -7838,15 +7883,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>4879964.1399999997</v>
+        <v>5177869.93</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>4108374.3899999997</v>
+        <v>4361349.18</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>9308.5499999999993</v>
+        <v>9411.34</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7854,11 +7899,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>28716</v>
+        <v>30864</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>4101773</v>
+        <v>4354645</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -12960,15 +13005,27 @@
       <c r="B33" s="24">
         <v>46258</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="27"/>
+      <c r="C33" s="28">
+        <v>522837.46</v>
+      </c>
+      <c r="D33" s="28">
+        <v>445207.46</v>
+      </c>
+      <c r="E33" s="27">
+        <v>138.46</v>
+      </c>
       <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="28"/>
+      <c r="G33" s="27">
+        <v>3096</v>
+      </c>
+      <c r="H33" s="28">
+        <v>445069</v>
+      </c>
       <c r="I33" s="27"/>
       <c r="J33" s="28"/>
-      <c r="K33" s="27"/>
+      <c r="K33" s="27">
+        <v>50</v>
+      </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="7"/>
@@ -13234,15 +13291,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>6291429.0599999996</v>
+        <v>6814266.5199999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>5385540.3099999996</v>
+        <v>5830747.7699999996</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>40764.39</v>
+        <v>40902.85</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -13250,11 +13307,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>31452</v>
+        <v>34548</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>4978908</v>
+        <v>5423977</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -13266,7 +13323,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>3476.13</v>
+        <v>3526.13</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0DFA4E-E12A-4159-A8AF-0012881B6A54}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A7A14F-9F6F-4318-9DC0-A8B161A05275}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -2223,12 +2223,22 @@
       <c r="B34" s="24">
         <v>46259</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
+      <c r="C34" s="28">
+        <v>780276</v>
+      </c>
+      <c r="D34" s="28">
+        <v>674364</v>
+      </c>
       <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="28"/>
+      <c r="F34" s="28">
+        <v>654</v>
+      </c>
+      <c r="G34" s="27">
+        <v>5172</v>
+      </c>
+      <c r="H34" s="28">
+        <v>675018</v>
+      </c>
       <c r="I34" s="27"/>
       <c r="J34" s="28"/>
       <c r="K34" s="27"/>
@@ -2469,11 +2479,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5482044.9299999997</v>
+        <v>6262320.9299999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>4495192.5</v>
+        <v>5169556.5</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -2481,15 +2491,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>710.92</v>
+        <v>1364.92</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>20646</v>
+        <v>25818</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>4529474.5</v>
+        <v>5204492.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7637,12 +7647,22 @@
       <c r="B34" s="24">
         <v>46259</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="27"/>
+      <c r="C34" s="28">
+        <v>522757.42</v>
+      </c>
+      <c r="D34" s="28">
+        <v>441359.17</v>
+      </c>
+      <c r="E34" s="27">
+        <v>1604.17</v>
+      </c>
       <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="28"/>
+      <c r="G34" s="27">
+        <v>4074</v>
+      </c>
+      <c r="H34" s="28">
+        <v>439755</v>
+      </c>
       <c r="I34" s="27"/>
       <c r="J34" s="28"/>
       <c r="K34" s="27"/>
@@ -7883,15 +7903,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>5177869.93</v>
+        <v>5700627.3499999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>4361349.18</v>
+        <v>4802708.3499999996</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>9411.34</v>
+        <v>11015.51</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7899,11 +7919,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>30864</v>
+        <v>34938</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>4354645</v>
+        <v>4794400</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -13045,12 +13065,22 @@
       <c r="B34" s="24">
         <v>46259</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
+      <c r="C34" s="28">
+        <v>660175.25</v>
+      </c>
+      <c r="D34" s="28">
+        <v>559954.25</v>
+      </c>
       <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="28"/>
+      <c r="F34" s="28">
+        <v>696.75</v>
+      </c>
+      <c r="G34" s="27">
+        <v>3882</v>
+      </c>
+      <c r="H34" s="28">
+        <v>560651</v>
+      </c>
       <c r="I34" s="27"/>
       <c r="J34" s="28"/>
       <c r="K34" s="27"/>
@@ -13291,11 +13321,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>6814266.5199999996</v>
+        <v>7474441.7699999996</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>5830747.7699999996</v>
+        <v>6390702.0199999996</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -13303,15 +13333,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>18409.079999999998</v>
+        <v>19105.829999999998</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>34548</v>
+        <v>38430</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>5423977</v>
+        <v>5984628</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A7A14F-9F6F-4318-9DC0-A8B161A05275}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BFCC7F-D90C-4FB1-B3E1-13CF325D426E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -2261,12 +2261,22 @@
       <c r="B35" s="24">
         <v>46260</v>
       </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="27"/>
+      <c r="C35" s="28">
+        <v>435322.33</v>
+      </c>
+      <c r="D35" s="28">
+        <v>361207.33</v>
+      </c>
+      <c r="E35" s="27">
+        <v>2318.33</v>
+      </c>
       <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="28"/>
+      <c r="G35" s="27">
+        <v>2772</v>
+      </c>
+      <c r="H35" s="28">
+        <v>358889</v>
+      </c>
       <c r="I35" s="27"/>
       <c r="J35" s="28"/>
       <c r="K35" s="27"/>
@@ -2479,15 +2489,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6262320.9299999997</v>
+        <v>6697643.2599999998</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>5169556.5</v>
+        <v>5530763.8300000001</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>6428.92</v>
+        <v>8747.25</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2495,11 +2505,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>25818</v>
+        <v>28590</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>5204492.5</v>
+        <v>5563381.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7685,12 +7695,22 @@
       <c r="B35" s="24">
         <v>46260</v>
       </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
+      <c r="C35" s="28">
+        <v>231766.54</v>
+      </c>
+      <c r="D35" s="28">
+        <v>198975.79</v>
+      </c>
       <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="28"/>
+      <c r="F35" s="28">
+        <v>947.21</v>
+      </c>
+      <c r="G35" s="27">
+        <v>300</v>
+      </c>
+      <c r="H35" s="28">
+        <v>199923</v>
+      </c>
       <c r="I35" s="27"/>
       <c r="J35" s="28"/>
       <c r="K35" s="27"/>
@@ -7903,11 +7923,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>5700627.3499999996</v>
+        <v>5932393.8899999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>4802708.3499999996</v>
+        <v>5001684.1399999997</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -7915,15 +7935,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>6469.17</v>
+        <v>7416.38</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>34938</v>
+        <v>35238</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>4794400</v>
+        <v>4994323</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -13103,15 +13123,25 @@
       <c r="B35" s="24">
         <v>46260</v>
       </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
+      <c r="C35" s="28">
+        <v>559694.17000000004</v>
+      </c>
+      <c r="D35" s="28">
+        <v>482839.67</v>
+      </c>
       <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
+      <c r="F35" s="28">
+        <v>717.33</v>
+      </c>
+      <c r="G35" s="27">
+        <v>2394</v>
+      </c>
       <c r="H35" s="28"/>
       <c r="I35" s="27"/>
       <c r="J35" s="28"/>
-      <c r="K35" s="27"/>
+      <c r="K35" s="27">
+        <v>50</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="7"/>
@@ -13321,11 +13351,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>7474441.7699999996</v>
+        <v>8034135.9399999995</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>6390702.0199999996</v>
+        <v>6873541.6899999995</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -13333,11 +13363,11 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>19105.829999999998</v>
+        <v>19823.16</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>38430</v>
+        <v>40824</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
@@ -13353,7 +13383,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>3526.13</v>
+        <v>3576.13</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BFCC7F-D90C-4FB1-B3E1-13CF325D426E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51795914-886D-4436-B7E8-78EAD452E225}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -267,6 +267,34 @@
           <t xml:space="preserve">
 SOUND CHECK
 S.I NO 11943
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I36" authorId="0" shapeId="0" xr:uid="{A387BDC5-C5C9-46DA-8247-8728B7555D4C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+C. TAMPUS
+S.I NO 12073
+SOUND CHECK
+S.I NO 12072
 </t>
         </r>
       </text>
@@ -2299,13 +2327,26 @@
       <c r="B36" s="24">
         <v>46261</v>
       </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="27"/>
+      <c r="C36" s="28">
+        <v>399906.63</v>
+      </c>
+      <c r="D36" s="28">
+        <v>85667.08</v>
+      </c>
+      <c r="E36" s="27">
+        <v>366.08</v>
+      </c>
       <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="27"/>
+      <c r="G36" s="27">
+        <v>1944</v>
+      </c>
+      <c r="H36" s="28">
+        <v>85331</v>
+      </c>
+      <c r="I36" s="27">
+        <f>223901+49474</f>
+        <v>273375</v>
+      </c>
       <c r="J36" s="28"/>
       <c r="K36" s="27"/>
       <c r="L36" s="1"/>
@@ -2489,15 +2530,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6697643.2599999998</v>
+        <v>7097549.8899999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>5530763.8300000001</v>
+        <v>5616430.9100000001</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>8747.25</v>
+        <v>9113.33</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2505,15 +2546,15 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>28590</v>
+        <v>30534</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>5563381.5</v>
+        <v>5648712.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>308112</v>
+        <v>581487</v>
       </c>
       <c r="J43" s="14">
         <f t="shared" si="1"/>
@@ -7733,12 +7774,22 @@
       <c r="B36" s="24">
         <v>46261</v>
       </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="27"/>
+      <c r="C36" s="28">
+        <v>270151.75</v>
+      </c>
+      <c r="D36" s="28">
+        <v>228277.75</v>
+      </c>
+      <c r="E36" s="27">
+        <v>482.75</v>
+      </c>
       <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="28"/>
+      <c r="G36" s="27">
+        <v>1356</v>
+      </c>
+      <c r="H36" s="28">
+        <v>227795</v>
+      </c>
       <c r="I36" s="27"/>
       <c r="J36" s="28"/>
       <c r="K36" s="27"/>
@@ -7923,15 +7974,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>5932393.8899999997</v>
+        <v>6202545.6399999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>5001684.1399999997</v>
+        <v>5229961.8899999997</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>11015.51</v>
+        <v>11498.26</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7939,11 +7990,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>35238</v>
+        <v>36594</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>4994323</v>
+        <v>5222118</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -13161,12 +13212,22 @@
       <c r="B36" s="24">
         <v>46261</v>
       </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
+      <c r="C36" s="28">
+        <v>379815.13</v>
+      </c>
+      <c r="D36" s="28">
+        <v>322965.88</v>
+      </c>
       <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="28"/>
+      <c r="F36" s="27">
+        <v>1201.1300000000001</v>
+      </c>
+      <c r="G36" s="27">
+        <v>2262</v>
+      </c>
+      <c r="H36" s="28">
+        <v>324167</v>
+      </c>
       <c r="I36" s="27"/>
       <c r="J36" s="28"/>
       <c r="K36" s="27"/>
@@ -13351,11 +13412,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>8034135.9399999995</v>
+        <v>8413951.0700000003</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>6873541.6899999995</v>
+        <v>7196507.5699999994</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -13363,15 +13424,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>19823.16</v>
+        <v>21024.29</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>40824</v>
+        <v>43086</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>5984628</v>
+        <v>6308795</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>

--- a/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
+++ b/GBDS AUGUST FILES 2026/SHORT OVER ALL ROUTES - AUGUST 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS AUGUST FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51795914-886D-4436-B7E8-78EAD452E225}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BE82FB-CCC8-46DF-B520-6C5CFCA7FE37}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="AUGUST, SRS R1" sheetId="6" r:id="rId1"/>
@@ -296,6 +296,62 @@
 SOUND CHECK
 S.I NO 12072
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I37" authorId="0" shapeId="0" xr:uid="{A0C1F776-F5D8-4FB8-8058-29B08CD874BA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+PROMO:
+*CATIG STORE 
+S.I NO 121079
+*BALAMBAN STORE
+S.I NO 12078
+*PIZON MINIMART
+S.I NO 12077
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J37" authorId="0" shapeId="0" xr:uid="{955EBD83-0760-4E50-A5D0-CA8EFC0D02EF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+TAMPUS STORE
+S.I NO ?</t>
         </r>
       </text>
     </comment>
@@ -2368,14 +2424,29 @@
       <c r="B37" s="24">
         <v>46262</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="27"/>
+      <c r="C37" s="28">
+        <v>837426</v>
+      </c>
+      <c r="D37" s="28">
+        <v>953828</v>
+      </c>
+      <c r="E37" s="27">
+        <v>1372</v>
+      </c>
       <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="28"/>
+      <c r="G37" s="27">
+        <v>4284</v>
+      </c>
+      <c r="H37" s="28">
+        <v>952456</v>
+      </c>
+      <c r="I37" s="27">
+        <f>5850+5850+3900</f>
+        <v>15600</v>
+      </c>
+      <c r="J37" s="28">
+        <v>223649</v>
+      </c>
       <c r="K37" s="27"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -2530,15 +2601,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>7097549.8899999997</v>
+        <v>7934975.8899999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>5616430.9100000001</v>
+        <v>6570258.9100000001</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>9113.33</v>
+        <v>10485.33</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -2546,19 +2617,19 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>30534</v>
+        <v>34818</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>5648712.5</v>
+        <v>6601168.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>581487</v>
+        <v>597087</v>
       </c>
       <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v>293109</v>
+        <v>516758</v>
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
@@ -7812,12 +7883,22 @@
       <c r="B37" s="24">
         <v>46262</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="27"/>
+      <c r="C37" s="28">
+        <v>237462</v>
+      </c>
+      <c r="D37" s="28">
+        <v>201220.5</v>
+      </c>
+      <c r="E37" s="27">
+        <v>771</v>
+      </c>
       <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="28"/>
+      <c r="G37" s="27">
+        <v>1356</v>
+      </c>
+      <c r="H37" s="28">
+        <v>200449.5</v>
+      </c>
       <c r="I37" s="27"/>
       <c r="J37" s="28"/>
       <c r="K37" s="27"/>
@@ -7974,15 +8055,15 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>6202545.6399999997</v>
+        <v>6440007.6399999997</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>5229961.8899999997</v>
+        <v>5431182.3899999997</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
-        <v>11498.26</v>
+        <v>12269.26</v>
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
@@ -7990,11 +8071,11 @@
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>36594</v>
+        <v>37950</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>5222118</v>
+        <v>5422567.5</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -13219,7 +13300,7 @@
         <v>322965.88</v>
       </c>
       <c r="E36" s="27"/>
-      <c r="F36" s="27">
+      <c r="F36" s="28">
         <v>1201.1300000000001</v>
       </c>
       <c r="G36" s="27">
@@ -13250,15 +13331,28 @@
       <c r="B37" s="24">
         <v>46262</v>
       </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
+      <c r="C37" s="28">
+        <f>335244</f>
+        <v>335244</v>
+      </c>
+      <c r="D37" s="28">
+        <v>285715</v>
+      </c>
       <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="28"/>
+      <c r="F37" s="28">
+        <v>22</v>
+      </c>
+      <c r="G37" s="27">
+        <v>1596</v>
+      </c>
+      <c r="H37" s="28">
+        <v>285737</v>
+      </c>
       <c r="I37" s="27"/>
       <c r="J37" s="28"/>
-      <c r="K37" s="27"/>
+      <c r="K37" s="27">
+        <v>50</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="8"/>
@@ -13412,11 +13506,11 @@
       <c r="B43" s="24"/>
       <c r="C43" s="14">
         <f t="shared" ref="C43:J43" si="0">SUM(C10:C42)</f>
-        <v>8413951.0700000003</v>
+        <v>8749195.0700000003</v>
       </c>
       <c r="D43" s="14">
         <f t="shared" si="0"/>
-        <v>7196507.5699999994</v>
+        <v>7482222.5699999994</v>
       </c>
       <c r="E43" s="25">
         <f t="shared" si="0"/>
@@ -13424,15 +13518,15 @@
       </c>
       <c r="F43" s="14">
         <f t="shared" si="0"/>
-        <v>21024.29</v>
+        <v>21046.29</v>
       </c>
       <c r="G43" s="25">
         <f t="shared" si="0"/>
-        <v>43086</v>
+        <v>44682</v>
       </c>
       <c r="H43" s="14">
         <f t="shared" si="0"/>
-        <v>6308795</v>
+        <v>6594532</v>
       </c>
       <c r="I43" s="25">
         <f t="shared" si="0"/>
@@ -13444,7 +13538,7 @@
       </c>
       <c r="K43" s="14">
         <f>SUM(K10:K42)</f>
-        <v>3576.13</v>
+        <v>3626.13</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
